--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126493143</v>
+        <v>126493121</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>79598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743157</v>
+        <v>743337</v>
       </c>
       <c r="R2" t="n">
-        <v>7200248</v>
+        <v>7200481</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126493121</v>
+        <v>126493143</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>91259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743337</v>
+        <v>743157</v>
       </c>
       <c r="R3" t="n">
-        <v>7200481</v>
+        <v>7200248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126493121</v>
+        <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>91259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743337</v>
+        <v>743157</v>
       </c>
       <c r="R2" t="n">
-        <v>7200481</v>
+        <v>7200248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126493143</v>
+        <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>79598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743157</v>
+        <v>743337</v>
       </c>
       <c r="R3" t="n">
-        <v>7200248</v>
+        <v>7200481</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126493157</v>
+        <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>92727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743299</v>
+        <v>743317</v>
       </c>
       <c r="R4" t="n">
-        <v>7200364</v>
+        <v>7200490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126493129</v>
+        <v>126493149</v>
       </c>
       <c r="B5" t="n">
-        <v>92727</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>743317</v>
+        <v>743194</v>
       </c>
       <c r="R5" t="n">
-        <v>7200490</v>
+        <v>7200379</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126493149</v>
+        <v>126493157</v>
       </c>
       <c r="B6" t="n">
         <v>78980</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>743194</v>
+        <v>743299</v>
       </c>
       <c r="R6" t="n">
-        <v>7200379</v>
+        <v>7200364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långa bålar, rikligt</t>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1466,7 +1466,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126493158</v>
+        <v>126493154</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743303</v>
+        <v>743198</v>
       </c>
       <c r="R10" t="n">
-        <v>7200365</v>
+        <v>7200290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1563,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126493154</v>
+        <v>126493158</v>
       </c>
       <c r="B11" t="n">
         <v>78980</v>
@@ -1603,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743198</v>
+        <v>743303</v>
       </c>
       <c r="R11" t="n">
-        <v>7200290</v>
+        <v>7200365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1639,6 +1634,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126493161</v>
+        <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,34 +1676,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klockarliden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>743253</v>
+        <v>743367</v>
       </c>
       <c r="R12" t="n">
-        <v>7200556</v>
+        <v>7200492</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,11 +1744,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126493126</v>
+        <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,42 +1781,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Klockarliden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>743367</v>
+        <v>743253</v>
       </c>
       <c r="R13" t="n">
-        <v>7200492</v>
+        <v>7200556</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,6 +1841,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126493141</v>
+        <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743375</v>
+        <v>743338</v>
       </c>
       <c r="R15" t="n">
-        <v>7200435</v>
+        <v>7200376</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2048,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126493130</v>
+        <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743338</v>
+        <v>743375</v>
       </c>
       <c r="R16" t="n">
-        <v>7200376</v>
+        <v>7200435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2146,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126493132</v>
+        <v>126493148</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2374,21 +2374,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>743333</v>
+        <v>743194</v>
       </c>
       <c r="R19" t="n">
-        <v>7200491</v>
+        <v>7200415</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2436,13 +2436,17 @@
           <t>2025-07-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långa bålar, riktigt</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2461,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126493148</v>
+        <v>126493132</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2496,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>743194</v>
+        <v>743333</v>
       </c>
       <c r="R20" t="n">
-        <v>7200415</v>
+        <v>7200491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,17 +2538,13 @@
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långa bålar, riktigt</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126493162</v>
+        <v>126493152</v>
       </c>
       <c r="B24" t="n">
         <v>78980</v>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>743208</v>
+        <v>743219</v>
       </c>
       <c r="R24" t="n">
-        <v>7200602</v>
+        <v>7200218</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2931,6 +2931,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,7 +2962,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126493152</v>
+        <v>126493162</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -2992,10 +2997,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>743219</v>
+        <v>743208</v>
       </c>
       <c r="R25" t="n">
-        <v>7200218</v>
+        <v>7200602</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3028,11 +3033,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långa bålar, rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,7 +3059,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126493153</v>
+        <v>126493151</v>
       </c>
       <c r="B26" t="n">
         <v>78980</v>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>743231</v>
+        <v>743234</v>
       </c>
       <c r="R26" t="n">
-        <v>7200246</v>
+        <v>7200207</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,10 +3263,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126493125</v>
+        <v>126493153</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3274,42 +3274,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Klockarliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>743193</v>
+        <v>743231</v>
       </c>
       <c r="R28" t="n">
-        <v>7200496</v>
+        <v>7200246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,7 +3338,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3373,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126493151</v>
+        <v>126493125</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3384,34 +3376,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klockarliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>743234</v>
+        <v>743193</v>
       </c>
       <c r="R29" t="n">
-        <v>7200207</v>
+        <v>7200496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt, långa bålar</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126493128</v>
+        <v>126493154</v>
       </c>
       <c r="B9" t="n">
-        <v>92727</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>743342</v>
+        <v>743198</v>
       </c>
       <c r="R9" t="n">
-        <v>7200476</v>
+        <v>7200290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126493154</v>
+        <v>126493158</v>
       </c>
       <c r="B10" t="n">
         <v>78980</v>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>743198</v>
+        <v>743303</v>
       </c>
       <c r="R10" t="n">
-        <v>7200290</v>
+        <v>7200365</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,6 +1537,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126493158</v>
+        <v>126493128</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>92727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>743303</v>
+        <v>743342</v>
       </c>
       <c r="R11" t="n">
-        <v>7200365</v>
+        <v>7200476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1639,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126493130</v>
+        <v>126493141</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743338</v>
+        <v>743375</v>
       </c>
       <c r="R15" t="n">
-        <v>7200376</v>
+        <v>7200435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2067,10 +2066,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126493141</v>
+        <v>126493130</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2078,21 +2077,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2101,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743375</v>
+        <v>743338</v>
       </c>
       <c r="R16" t="n">
-        <v>7200435</v>
+        <v>7200376</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,6 +2145,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -1969,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126493141</v>
+        <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>743375</v>
+        <v>743338</v>
       </c>
       <c r="R15" t="n">
-        <v>7200435</v>
+        <v>7200376</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2048,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2066,10 +2067,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126493130</v>
+        <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,21 +2078,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2101,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>743338</v>
+        <v>743375</v>
       </c>
       <c r="R16" t="n">
-        <v>7200376</v>
+        <v>7200435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,7 +2146,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>91518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>92727</v>
+        <v>92989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1064,14 +1076,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,14 +1182,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,14 +1288,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,14 +1389,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>92727</v>
+        <v>92989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,14 +1490,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,14 +1591,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,14 +1697,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>57654</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,14 +1806,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,14 +1912,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1965,14 +2013,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78878</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,14 +2115,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>78877</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,14 +2216,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,14 +2322,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,14 +2423,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>78878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,14 +2525,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2559,14 +2631,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2661,14 +2737,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2758,14 +2838,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>78878</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,14 +2940,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,14 +3046,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,14 +3147,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3157,14 +3253,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,14 +3359,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126493125</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,14 +3473,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3471,14 +3579,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3568,14 +3680,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>92727</v>
+        <v>92989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3665,14 +3781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78738</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,14 +3882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,7 +3988,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126493125</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126493125</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91537</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126493125</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126493126</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>126493125</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126493121</v>
       </c>
       <c r="B3" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126493157</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>126493149</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>126493159</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126493119</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>126493154</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>126493158</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>126493161</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>126493118</v>
       </c>
       <c r="B14" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126493130</v>
       </c>
       <c r="B15" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>126493141</v>
       </c>
       <c r="B16" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>126493147</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>126493116</v>
       </c>
       <c r="B18" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>126493132</v>
       </c>
       <c r="B19" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>126493148</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,7 +2642,7 @@
         <v>126493156</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>126493150</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>126493131</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>126493152</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>126493162</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>126493153</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>126493144</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         <v>126493151</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>126493142</v>
       </c>
       <c r="B32" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>126493155</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 31759-2025 artfynd.xlsx
+++ b/artfynd/A 31759-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493143</v>
       </c>
       <c r="B2" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126493129</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>126493128</v>
       </c>
       <c r="B9" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>126493115</v>
       </c>
       <c r="B30" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>126493127</v>
       </c>
       <c r="B31" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
